--- a/AAII_Financials/Quarterly/CAIXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAIXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="92">
   <si>
     <t>CAIXY</t>
   </si>
@@ -656,71 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +766,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +813,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +860,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +881,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +926,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +973,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1020,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1067,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1085,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1130,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1177,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1198,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1243,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1290,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1337,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1384,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1431,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1478,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1525,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1572,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1619,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1666,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1713,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1760,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1807,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1854,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1901,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +1948,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2021,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,404 +2040,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4448800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4330200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>63003600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4325300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3984900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69614100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4746600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4594900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44740700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4594900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44740700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4577500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>38974400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4422400</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8829000</v>
+      </c>
+      <c r="E42" s="3">
         <v>20702100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9240900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10103300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15964400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15913500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8113100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8801800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30407500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8801800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30407500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9162700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9637100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8647000</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4262500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3338000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3">
         <v>3799200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2926800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>1766800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2133300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
         <v>2181900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>1653900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>2929400</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1378400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1356300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1133300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1621300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1670800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1261100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>804700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1786600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>804700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1786600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>760900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1983900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>938300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1299000</v>
+      </c>
+      <c r="E45" s="3">
         <v>773700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>307400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>792700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>545600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>428300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>906500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3358000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>620200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3309400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>620200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1815500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>593200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2669700</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57940100</v>
+      </c>
+      <c r="E46" s="3">
         <v>80828900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73908200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73597200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>73440300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>87626600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>69898200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>56947100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>77555000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>56947100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>77555000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>58921400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>51188600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>37116600</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>231802800</v>
+      </c>
+      <c r="E47" s="3">
         <v>221760000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>218863100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>215534900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>180586000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>183565700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>182091500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187961800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>156694500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>187961800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>156694500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>187254400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>187957400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>178271900</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6363500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6610300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7872800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6635300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5913700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7898700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6237000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6496100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7731800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6496100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7731800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6466200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8179100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6325700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6045900</v>
+      </c>
+      <c r="E49" s="3">
         <v>6186500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6015500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5985900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5252100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5557700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5313400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5512300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5313300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5512300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5313300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5459600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5428100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5369200</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2508,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2555,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1786800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1886800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21863200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2735200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2237300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21433200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2508300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3281800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21597200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3281800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21597200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3680100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22668400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3774700</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2649,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>792218700</v>
+      </c>
+      <c r="E54" s="3">
         <v>779664200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>780240500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>774893700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>653279800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>709103300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>675421600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>671125200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>647119000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>671125200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>647119000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>682966200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>672216400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>640002100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2717,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2736,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>565620900</v>
+      </c>
+      <c r="E57" s="3">
         <v>522369400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>550765000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>550756300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>438961600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>488749700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>476942000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>441784000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>452778400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>441784000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>452778400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>487162700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>477948700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>455117000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6277800</v>
+      </c>
+      <c r="E58" s="3">
         <v>38441900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4090100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8575500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22606900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1603800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6477000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>30361400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4296100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>30361400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4296100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6316600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4297000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6416600</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4649800</v>
+      </c>
+      <c r="E59" s="3">
         <v>7087000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
         <v>4052800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6045100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>3461900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6113600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>6113600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>2491300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3703800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4818900</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>576548600</v>
+      </c>
+      <c r="E60" s="3">
         <v>567898300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>554855100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>563384600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>467613600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>490353600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>486881000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>478259100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>457074500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>478259100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>457074500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>495970500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>485949600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>466352500</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58696400</v>
+      </c>
+      <c r="E61" s="3">
         <v>63069200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>60057500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>60098600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>60188400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>63740800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58329600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>64568400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>60205300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>64568400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>60205300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>57866800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>55474800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57941600</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>109909700</v>
+      </c>
+      <c r="E62" s="3">
         <v>101807000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>120151400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>99349400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>85605100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>113727400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>84162600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>85944500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>92442800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85944500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>92442800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>83643000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>94901100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>77357100</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3063,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3110,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3157,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>748009800</v>
+      </c>
+      <c r="E66" s="3">
         <v>734430000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>735063900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>730928900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>615112300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>667821800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>637391000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>630958300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>609722700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>630958300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>609722700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>645799100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>636325500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>603978800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3225,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3270,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3317,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3364,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3411,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27442000</v>
+      </c>
+      <c r="E72" s="3">
         <v>27190300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5159000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25153300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21228900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4737900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19748200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21820500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>21820500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>18632100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>17934200</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3505,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3552,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3599,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44192800</v>
+      </c>
+      <c r="E76" s="3">
         <v>45215500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45161300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>43951800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38132300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>41244700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37996400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40131500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37361300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40131500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37361300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37132100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35855100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>35989100</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3693,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3792,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,8 +3813,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3660,8 +3858,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +3905,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +3952,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +3999,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4046,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,8 +4093,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3924,8 +4140,11 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,8 +4161,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3986,8 +4206,11 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4253,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,8 +4300,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4118,8 +4347,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,8 +4368,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4180,8 +4413,11 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4460,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4507,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,8 +4554,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4356,8 +4601,11 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4400,8 +4648,11 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4442,6 +4693,9 @@
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
